--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260818.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260818.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.54%</t>
+          <t>9.97%</t>
         </is>
       </c>
     </row>
@@ -638,51 +638,51 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.41%</t>
+          <t>9.51%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>38,830,000</t>
+          <t>370,440,486</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.80%</t>
+          <t>6.03%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>370,440,486</t>
+          <t>38,830,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.79%</t>
+          <t>5.80%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.02%</t>
+          <t>4.26%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>3.66%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.65%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.23%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.16%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.97%</t>
         </is>
       </c>
     </row>
@@ -836,139 +836,139 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.89%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>360,120,964</t>
+          <t>131,951,945</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>131,951,945</t>
+          <t>360,120,964</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>26,219,000</t>
+          <t>31,356,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.60%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>98,298,442</t>
+          <t>26,219,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.58%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>31,356,000</t>
+          <t>199,761,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>83,020,000</t>
+          <t>98,298,442</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
@@ -985,78 +985,78 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>227,363,516</t>
+          <t>236,458,056</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>199,761,000</t>
+          <t>83,020,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>131,081,000</t>
+          <t>145,204,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>145,204,000</t>
+          <t>131,081,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.23%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
@@ -1144,51 +1144,51 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>202609TX</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>1,274</t>
+          <t>54,488,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>202609TX</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>54,488,000</t>
+          <t>1,274</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.87%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.68%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>22,762,660,056</t>
+          <t>26,084,565,032</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>5,003,111,202</t>
+          <t>4,790,098,402</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-404,917,552</t>
+          <t>-459,541,339</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
